--- a/Creacion_baremos/muestra_seleccionada_500.xlsx
+++ b/Creacion_baremos/muestra_seleccionada_500.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B501"/>
+  <dimension ref="A1:A501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -422,5010 +422,2505 @@
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>NOMBRE COMPLETO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>2026119210</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BARRANCOS ECHEVERRIA AUGUSTA MONSERRAT</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2018117840</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>PABON JURADO MANUEL ALEJANDRO</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>2025115105</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ESCOBAR BANEGAS FRIDA SOFIA</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>2023116031</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SAAVEDRA PADILLA MARIA FERNANDA</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>2023117780</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BRAVO ROCA MICAELA</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>2023210101</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>CUBA BRUNO JUAN ANTONIO</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>2022111885</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>GARCIA TORRICO FRANK ANTHONY</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>2024110991</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>LOPEZ TORRICO HANSSEL OLIVER</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>2026116971</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>MELGAR RODRIGUEZ LUCIANA</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>2022116372</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>MARTINEZ VERDUGUEZ HEIDDY NICOLE</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>2022112580</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>LOPEZ UGARTECHE MARIA ALEJANDRA</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>2022111257</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>FLORES VARGAS PEDRO ENRIQUE</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>2026116229</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>AMELUNGE DE MIGUEL JOAQUIN</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>2019210916</v>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>LARRAIN PINTO MARÍA FERNANDA</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>2024211518</v>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>BEDREGAL BALDIVIESO ANA CECILIA</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>2025112670</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>RIVERA ALVAREZ ZULEIKA NAOMI</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>2022112547</v>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>RIOS PINTO SEBASTIAN ALEXANDRE</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>2021114660</v>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>AGUILERA ARIAS DIEGO ALESSANDRO</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>2025110294</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>SALDAÑA LETELIER MARÍA VICTORIA</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>2022116992</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ORDOÑEZ BARZON DANIEL</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>2026117241</v>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>CALDERON CARVAJAL JAIME IGNACIO</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>2021112101</v>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>PINEDO MORENO LUCAS MATIAS</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>2025115237</v>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>ORELLANA DE URIOSTE MARTIN OMAR</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>2024114059</v>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>VASQUEZ MUÑOZ LUZ SHEDENKA</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>2023212111</v>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>ROJAS LANDIVAR WILSON</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>2024111742</v>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>LLUSCO LOPEZ ANYI LAURA</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>2023111986</v>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>ECHAZU ROMAN FABIANA</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>2022110676</v>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>ANTELO MEDINA ALEXANDER</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>2025112131</v>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>ZARZA ARANDIA JOSELINE</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>2024110495</v>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>OSINAGA ARGANDOÑA FREDSIL ABIGAIL</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>2026115842</v>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>SEIWALD SALAZAR CRISTIAN SEBASTIAN</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>2022112148</v>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>CRUZ GUZMAN MELINA</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>2024112765</v>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>SOMMER MIRAMENDI DUSTIN JAROSLAV</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>2023112699</v>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>RODRIGUEZ MONTAÑO MIGUEL ANGELO</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>2022116585</v>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>AGUILAR SAUCEDO FABIANA SIOMARA</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>2026113513</v>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>PEÑA SUAREZ ROBERTO CARLOS</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>2026112029</v>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>FERNANDEZ TORRES PAUL SIMON</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>2024115411</v>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>OLIVEIRA ZAMBON ODILON ANTONIO</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>2025212101</v>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>CARVAJAL CHOQUE VIVIANA BELEN</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>2026110468</v>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>PARRA REYNAGA BRANDON</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
         <v>2022114230</v>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>CALANI SALAS BELEN NAZARET</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
         <v>2026116202</v>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>CHAVEZ PAREDES NICOLAS</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>2025212038</v>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>MANSILLA FLORES ALEJANDRO</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>2026210071</v>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>ESPINOZA CASTELLON FABIO GAEL</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>2024117317</v>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>SOLARES LANDIVAR DANIEL IGNACIO</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>2018117637</v>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>BRINCKHAUS OLLER PHILLIPS JAIME</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>2025115156</v>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>KNEZ RIC SAMUEL</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>2026120200</v>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>ABBAS ROCA SALMA</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>2024113320</v>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>VELASCO CANDIA NOEMI MEL</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
         <v>2022117760</v>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>VARGAS MONASTERIO LEANDRO JHOAN</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>2025110952</v>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>CASTELLON ROCABADO SAMANTHA</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
         <v>2026113939</v>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>TORRICO CAREVIC JOSE CARLOS</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>2026112151</v>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>LORENT RODRIGUEZ ERICK ECKEHARD</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
         <v>2023116058</v>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>BIRBUET SANCHEZ CARMEN ALICIA</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>2023111587</v>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>ALDUNATE ESTRADA ALEXA MISHELL</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
         <v>2026114293</v>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>BARRIGA VEGA ELIEZER EBERT</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
         <v>2026114552</v>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>MONASTERIO SANTAMARIA SANTIAGO</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
         <v>2024116043</v>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>FRANZHEK RIVAS FIORELLA</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
         <v>2023120039</v>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>PEÑA BARRIENTOS JOSE DANIEL</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
         <v>2025112327</v>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>OLMOS PINO SOFIA BELÉN</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>2023112478</v>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>SUAREZ HINOJOSA MARIA FERNANDA</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
         <v>2024115799</v>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>CASTEDO BANZER MILENA</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
         <v>2025112726</v>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>PERALTA TUDOR MARIANA NOELIA</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
         <v>2021114813</v>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>CAMPOS VACA CARLA PATRICIA</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
         <v>2025111363</v>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>SOLETO VACA MARIA JOSE</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
         <v>2026211621</v>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>MURILLO CESPEDES ASHLEY ROSE</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
         <v>2022111818</v>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>VARGAS TORRICO JUAN JOSE</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
         <v>2023114331</v>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>PEREDO BALCAZAR NATHALIA</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
         <v>2026119911</v>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>CHAMBILLA QUISPE BLANCA JENIFER</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
         <v>2026120731</v>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>SANCHEZ ARIAS LEONEL</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
         <v>2024119786</v>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>PAN JEREZ ROY SHIAN</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
         <v>2026113751</v>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>AGUIRRE BALDOMAR SEBASTIAN</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
         <v>2022110536</v>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>PADILLA SANDOVAL LEONARDO</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
         <v>2025211953</v>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>RODRIGUEZ PADILLA AYLIN CAMILA</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
         <v>2025113773</v>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>HE YU VICTOR MINCE</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
         <v>2025110031</v>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>ROJAS PAZ NICOLÁS</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
         <v>2023115680</v>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>TORREZ CRESPO HELEN NICOL</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
         <v>2025110898</v>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>SOLETO ORTIZ CARLOS</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
         <v>2026115931</v>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>SUAREZ COIMBRA MARIA JOSE</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
         <v>2023113211</v>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>CABALLERO VARGAS ANDRES</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
         <v>2026113262</v>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>BANEGAS VACA JOSE GUILLERMO</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
         <v>2026112231</v>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>MOLINA OBLITAS SERGIO ANDRÉS</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
         <v>2023110629</v>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>DREW PUÑA ARIANA</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
         <v>2023110904</v>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>MONASTERIO MENASHE ELYNOR</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
         <v>2023211875</v>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>CRESPO FERNANDEZ JAIME ADRIAN</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
         <v>2023115001</v>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>PIMENTEL OLIVERA NATALY KAORY</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
         <v>2023111099</v>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>RAMOS MURILLO ARACELY</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
         <v>2025113285</v>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>YAMASHIRO GARCIA MISHERY</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
         <v>2025111576</v>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>CARVAJAL CASTEDO LUCIANA</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
         <v>2026115486</v>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>GUZMAN VILLARROEL LUCIANA</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
         <v>2026112797</v>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>INOFUENTES TERCEROS ARIANA MELANIE</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
         <v>2025113447</v>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>GUARDIA GIL RICARDO</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
         <v>2025111983</v>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>CONDORI ALVAREZ MAURICIO ALEXANDER</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
         <v>2025114893</v>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>ALVAREZ FLORES JULIANA</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
         <v>2025117345</v>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>ALEJANDRO COPA LIZBETH</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
         <v>2024111441</v>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>LEA PLAZA SOLIZ WALTER NICOLAS</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
         <v>2022114329</v>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>VALDIVIA CHOQUE DANIEL</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
         <v>2015113428</v>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>GUMUCIO ARIAS PAULA GABRIELA</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
         <v>2017115304</v>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>AYALA MILLAN ANDRES ANTONIO</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
         <v>2026119988</v>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>ZENTENO ALARCON VALERIA ANAHI</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
         <v>2022115279</v>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>BENITEZ RODRIGUEZ ROUSS DAYNA</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
         <v>2023111617</v>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>MALDONADO ANCARI BRISEI SELENE</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
         <v>2024110932</v>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>ILLESCAS MONTERO SILVIO ANDRES</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
         <v>2026110913</v>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>YABETA RAPPU ANDREA</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
         <v>2025117329</v>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>CLAROS CABRERA RICHARD EMANUEL</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
         <v>2024111769</v>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>SOTO CALUSTRO ELIANA</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
         <v>2023114969</v>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>JUSTINIANO RODAS MARIANA</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
         <v>2023114802</v>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>PANADERO ROJAS GONZALO</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
         <v>2026111707</v>
       </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>CONDORI CHOQUE JOSUE ALEJANDRO</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
         <v>2025111193</v>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>ARNEZ LOPEZ STEPHANIE</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
         <v>2022112563</v>
       </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>YRIGOYEN DAVALOS ALVARO</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
         <v>2024117180</v>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>TORRICO MEDINA SARINA</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
         <v>2025211660</v>
       </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>FRONTANILLA SANCHEZ MIA VALENTINA</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
         <v>2025116632</v>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>HERRERA RIVERO SAMARA</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
         <v>2026212511</v>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>MARQUEZ PEREZ RICARDO ANDRES</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
         <v>2026110948</v>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>MERCADO ISOLA LUCIANA</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
         <v>2024113036</v>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>GUTIERREZ FUENTES ALFREDO</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
         <v>2026126704</v>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>FERREYRA RALDES LUCAS GABRIEL</t>
-        </is>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
         <v>2022112415</v>
       </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>DAZA BENSAID RANIA</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
         <v>2024110312</v>
       </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>GARCIA DORADO GUSTAVO ISRAEL</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
         <v>2021110559</v>
       </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>KADIMA MORENO JOSE MIGUEL</t>
-        </is>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
         <v>2025113536</v>
       </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>ORTIZ AGUERO CAROLINA</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
         <v>2024111076</v>
       </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>CABRERA ARDAYA MAURICIO</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
         <v>2024112773</v>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>TOYOSATO MEDINA AKEMI ANDIARA</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
         <v>2026213305</v>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>FERRARA PAZ ALESSANDRO</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
         <v>2022116402</v>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>LENZ TINEO YASHA ROMMELLA</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
         <v>2026112339</v>
       </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>BALDOMAR SALAS JUAN CARLOS</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
         <v>2022111681</v>
       </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>ROCA PAZ GUILLERMO WILBER</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
         <v>2023115701</v>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>TEJERINA RUIZ SHARMEL ARIANNA</t>
-        </is>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
         <v>2023113083</v>
       </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>GUZMAN MOLINA MIGUEL ALEJANDRO</t>
-        </is>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
         <v>2022112997</v>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>NAZRALA HURTADO CARLOS ELIAS</t>
-        </is>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
         <v>2021212050</v>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>AGUILAR RAMOS RUBI LADY</t>
-        </is>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
         <v>2022114914</v>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>PACHECO PAREDES LUNA NOELIA</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
         <v>2021116620</v>
       </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>MISERENDINO MENDEZ MICHELLE BRENIZE</t>
-        </is>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
         <v>2025116659</v>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>SAUCEDO PEÑA ISABELLA</t>
-        </is>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
         <v>2022116313</v>
       </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>SUAREZ ANTELO NICOLAS</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
         <v>2025111266</v>
       </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>BASCOPE MIRANDA DIEGO FABRICIO</t>
-        </is>
-      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
         <v>2018113119</v>
       </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>BORDA ORTIZ MARIA JOSE</t>
-        </is>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
         <v>2023114861</v>
       </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>ARCE GIORGETTI MAURICIO</t>
-        </is>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
         <v>2026114137</v>
       </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>MONTAÑO ANIVARRO NATALIA</t>
-        </is>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
         <v>2024115951</v>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>JIMENEZ GAMARRA MARIANA</t>
-        </is>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
         <v>2025116730</v>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>VACA GONZALES LUCAS SANTIAGO</t>
-        </is>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
         <v>2025112467</v>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>ANTELO SANCHEZ LEONARDO</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
         <v>2022117034</v>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>ANZOATEGUI NUÑEZ ROSANGELA</t>
-        </is>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
         <v>2026115273</v>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>MANZONI BRAVO LUIS ALFREDO</t>
-        </is>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
         <v>2026111928</v>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>CAMPOS ARANCIBIA CAMILA</t>
-        </is>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
         <v>2023112460</v>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>LICHTENSTEIN BECERRA SEBASTIAN</t>
-        </is>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
         <v>2022111788</v>
       </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>ARCIENEGA EG▄EZ SERGIO ANDRÉS</t>
-        </is>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
         <v>2025210582</v>
       </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>SANCHEZ AGUIRRE LAURA</t>
-        </is>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
         <v>2024115241</v>
       </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>MELGAR SALAS SANTIAGO</t>
-        </is>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
         <v>2022114566</v>
       </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>ROCA QUINTELA SAMUEL</t>
-        </is>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
         <v>2024116795</v>
       </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>GUTIERREZ BRACAMONTE KAREN FATIMA</t>
-        </is>
-      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
         <v>2024116434</v>
       </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>YAÑEZ BEJARANO JOAQUIN</t>
-        </is>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
         <v>2025116551</v>
       </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>TERAN TAPIA FERNANDO ADRIAN</t>
-        </is>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
         <v>2024111751</v>
       </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>PARADA BECERRA ROMINA</t>
-        </is>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
         <v>2026110905</v>
       </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>ROJAS AREVALO ANDRES YUNIOR</t>
-        </is>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
         <v>2022111206</v>
       </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>GUTIERREZ ARANIBAR LAURA VERONICA</t>
-        </is>
-      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
         <v>2023111340</v>
       </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>BARBERY GARCIA JOSE ENRIQUE</t>
-        </is>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
         <v>2024118224</v>
       </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>TELLEZ RICO ABIGAIL</t>
-        </is>
-      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
         <v>2025112084</v>
       </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>PEREZ HERRERA DIANA CAMILA</t>
-        </is>
-      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
         <v>2024115381</v>
       </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>FRANCO ZABALETA NOEMI ALEJANDRA</t>
-        </is>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
         <v>2025113111</v>
       </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>ZABALA VELARDE NAZARENA</t>
-        </is>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
         <v>2024115802</v>
       </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>CHAMBI TERRAZAS MARSHELI ALISON</t>
-        </is>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
         <v>2024111521</v>
       </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>ORELLANA FERNANDEZ ISAAC</t>
-        </is>
-      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
         <v>2024113109</v>
       </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>MICHEL VACA MATIAS</t>
-        </is>
-      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
         <v>2024111271</v>
       </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>SUAREZ VACA MARCOS</t>
-        </is>
-      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
         <v>2026114838</v>
       </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>TORREZ ALVIS ARIANA</t>
-        </is>
-      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
         <v>2023111013</v>
       </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>LUCAS GRAGEDA MARIANNE</t>
-        </is>
-      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
         <v>2025211988</v>
       </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>GRAÑA PIRO THYARA KATHERINE</t>
-        </is>
-      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
         <v>2022114256</v>
       </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>CUELLAR FRANCO CAMILA</t>
-        </is>
-      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
         <v>2026117870</v>
       </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>PADILLA SUAREZ HELEN</t>
-        </is>
-      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
         <v>2026111201</v>
       </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>TERRAZAS CABALLERO RAQUEL</t>
-        </is>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
         <v>2026111693</v>
       </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>PALMA VELASCO CESAR MATEO</t>
-        </is>
-      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
         <v>2023112249</v>
       </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>SOLIZ IBAÑEZ SOFIA</t>
-        </is>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
         <v>2025115539</v>
       </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>VALLEJOS ROMAN JOSE RAFAEL</t>
-        </is>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
         <v>2023110050</v>
       </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>AÑEZ MONTOYA NATALIA</t>
-        </is>
-      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
         <v>2023111404</v>
       </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>RODRIGUEZ MORALES RODRIGO</t>
-        </is>
-      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
         <v>2020119021</v>
       </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>DUCHEN ABREGO GRECIA ALEJANDRA</t>
-        </is>
-      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
         <v>2026113203</v>
       </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>OLGUIN ESPADA SEBASTIAN ANDRES</t>
-        </is>
-      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
         <v>2025113064</v>
       </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>ANTELO DAVALOS ADRIAN LEONARDO</t>
-        </is>
-      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
         <v>2026114714</v>
       </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>ZEPITA ALDANA LUCERO</t>
-        </is>
-      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
         <v>2022115929</v>
       </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>CASTRO EG▄EZ OSCAR BRUNO</t>
-        </is>
-      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
         <v>2023111242</v>
       </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>AGUILERA BRAVO FABRICIO</t>
-        </is>
-      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
         <v>2021113493</v>
       </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>ZEBALLOS RIVERO YISELA KAROLAY</t>
-        </is>
-      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
         <v>2026118086</v>
       </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>VALVERDE SILES CARLOS EDUARDO</t>
-        </is>
-      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
         <v>2022112041</v>
       </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>CAMACHO MERCADO SEBASTIAN NICOLAS</t>
-        </is>
-      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
         <v>2026113807</v>
       </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>FIORILO MELGAR BRITTANY</t>
-        </is>
-      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
         <v>2026110301</v>
       </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>IBAÑEZ LÓPEZ ALEJANDRO MANUEL</t>
-        </is>
-      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
         <v>2019114488</v>
       </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>SANDOVAL RIBERA IAN</t>
-        </is>
-      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
         <v>2024111068</v>
       </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>ORTEGA AGUILERA CRISTHIAN ERNESTO</t>
-        </is>
-      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
         <v>2025111622</v>
       </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>PEREZ QUINTELA SANTIAGO</t>
-        </is>
-      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
         <v>2024116540</v>
       </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>DIAZ MATTA GALARZA ANDREA</t>
-        </is>
-      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
         <v>2023118620</v>
       </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>ALVAREZ LENS JESUS ANDRES</t>
-        </is>
-      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
         <v>2021116263</v>
       </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>GONZALES HOLLWEG NOELIA</t>
-        </is>
-      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
         <v>2026113521</v>
       </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>OJEDA JUSTINIANO AARON LEANDRO</t>
-        </is>
-      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
         <v>2023110238</v>
       </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>OLMOS ORTUSTE MARCO MATEO</t>
-        </is>
-      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
         <v>2026112169</v>
       </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>ZABALAGA SALAS CRISTIAN IGNACIO</t>
-        </is>
-      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
         <v>2024113117</v>
       </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>BAUER CASTEDO CARLOS ENRIQUE</t>
-        </is>
-      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
         <v>2026117527</v>
       </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>LARA ROMERO CAMILA</t>
-        </is>
-      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
         <v>2022211464</v>
       </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>TOMICHA ROCHA CARLOS ENRIQUE</t>
-        </is>
-      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
         <v>2026110107</v>
       </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>GROSS RAMIREZ ADRIANA DANIELA</t>
-        </is>
-      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
         <v>2026113742</v>
       </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>VARGAS SILVA SISSI ROCHEL</t>
-        </is>
-      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
         <v>2023115086</v>
       </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>OSINAGA ZURITA ANDRES DANIEL</t>
-        </is>
-      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
         <v>2025112378</v>
       </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>PARDO RAMIREZ DIEGO ARMANDO</t>
-        </is>
-      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
         <v>2026111006</v>
       </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>ROBLES SALVATIERRA LEE SANTIAGO</t>
-        </is>
-      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
         <v>2016115980</v>
       </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>FABIANI ORTIZ FABRICIO</t>
-        </is>
-      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
         <v>2024114199</v>
       </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>LUTHER CAMACHO LIZ MEL</t>
-        </is>
-      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
         <v>2025114605</v>
       </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>LINO RODRIGUEZ OSCAR MARIO</t>
-        </is>
-      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
         <v>2026110743</v>
       </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>CALLAU GOMEZ NICOLAS</t>
-        </is>
-      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
         <v>2017119644</v>
       </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>DEL GRANADO BARRANCOS LUIS CARLOS</t>
-        </is>
-      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
         <v>2022113373</v>
       </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>SALAS GUTIERREZ CARLA ANDREA</t>
-        </is>
-      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
         <v>2026116512</v>
       </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>REGUERIN CESPEDES JESENIA</t>
-        </is>
-      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
         <v>2026116423</v>
       </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>VALDEZ VELIT MASSIMO CAETANO</t>
-        </is>
-      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
         <v>2025111827</v>
       </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>ORTEGA AGUILAR KEYTLIN RASHEL</t>
-        </is>
-      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
         <v>2026118361</v>
       </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>XU VALENTINO ERWIN</t>
-        </is>
-      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
         <v>2024111351</v>
       </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>LUJAN CAMACHO LUCAS MATIAS</t>
-        </is>
-      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
         <v>2024113575</v>
       </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>SOLIZ ESCOBAR ANTONELLA</t>
-        </is>
-      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
         <v>2025110201</v>
       </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>RUIZ CARRASCO SEBASTIAN</t>
-        </is>
-      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
         <v>2026210080</v>
       </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>ROCHA MORET DANA ISABEL</t>
-        </is>
-      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
         <v>2025111533</v>
       </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>ARANIBAR POMA DARIO FRANCO</t>
-        </is>
-      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
         <v>2022118235</v>
       </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>ARDUZ GARECA JOHANN LUCA</t>
-        </is>
-      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
         <v>2024116671</v>
       </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>GUZMAN MOSCIARO ISABEL</t>
-        </is>
-      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
         <v>2023111846</v>
       </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>COCA ZEBALLOS MARIELY</t>
-        </is>
-      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
         <v>2026112789</v>
       </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>MENACHO PAZ SANTIAGO</t>
-        </is>
-      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
         <v>2025119267</v>
       </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>SUAREZ HEREDIA LUCIANA</t>
-        </is>
-      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
         <v>2026112355</v>
       </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>CESPEDES VIERA BRAYAN SEBASTIAN</t>
-        </is>
-      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
         <v>2022115538</v>
       </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>ASBUN MERCADO SABRINA</t>
-        </is>
-      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
         <v>2023213011</v>
       </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>SALVADOR UMALLA ALEJANDRA</t>
-        </is>
-      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
         <v>2022110293</v>
       </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>CAMACHO ORTIZ SANTIAGO GABRIEL</t>
-        </is>
-      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
         <v>2022111419</v>
       </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>PAZ ERGUETA MAURO</t>
-        </is>
-      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
         <v>2023112141</v>
       </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>MIRANDA PEREZ PAOLA ANDREA</t>
-        </is>
-      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
         <v>2025116217</v>
       </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>PEREZ FILIPOVICH SEBASTIAN</t>
-        </is>
-      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
         <v>2023112591</v>
       </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>BELTRAN RIVERA BEIMAR AARON</t>
-        </is>
-      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
         <v>2022212185</v>
       </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>SAAVEDRA DELLIEN LUCIANA</t>
-        </is>
-      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
         <v>2021113795</v>
       </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>AGUIRRE SALAZAR MIYEN</t>
-        </is>
-      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
         <v>2022110498</v>
       </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>GUERRERO ONTIVEROS YULENA NYCOLE</t>
-        </is>
-      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
         <v>2024111530</v>
       </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>PARADA PAZ MARIANA</t>
-        </is>
-      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
         <v>2022114981</v>
       </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>PEDRAZA PEREYRA ANGELA MARIA</t>
-        </is>
-      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
         <v>2021115216</v>
       </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>TERAN EGUEZ ALESSA</t>
-        </is>
-      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
         <v>2022110943</v>
       </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>JAUREGUI CASTEDO SOFIA</t>
-        </is>
-      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
         <v>2023115426</v>
       </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>HERNANDEZ VALVERDE CECILIA VANESSA</t>
-        </is>
-      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
         <v>2025117647</v>
       </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>VIDAL SAAVEDRA CINTIA MARIA</t>
-        </is>
-      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
         <v>2021111563</v>
       </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>CARDENAS CLAROS NICOLAS</t>
-        </is>
-      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
         <v>2022111907</v>
       </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>KRAYASICH ULLOA ALEXANDRA</t>
-        </is>
-      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
         <v>2026110557</v>
       </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>SORIA BORJA IVAN</t>
-        </is>
-      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
         <v>2024112200</v>
       </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>VARGAS PANIQUE ALISON BELEN</t>
-        </is>
-      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
         <v>2026118604</v>
       </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>ROSALES PERALTA JOSE ADALID</t>
-        </is>
-      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
         <v>2022115376</v>
       </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>LI LI WEISONG</t>
-        </is>
-      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
         <v>2026113459</v>
       </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>DIEZ DE MEDINA ANTELO MIA VICTORIA</t>
-        </is>
-      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
         <v>2023210798</v>
       </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>ADRIAZOLA BOEHME NATALIA</t>
-        </is>
-      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
         <v>2026115923</v>
       </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>SALAS GUARDIA LUCIANA EMILY</t>
-        </is>
-      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
         <v>2025118368</v>
       </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>QUINTEROS SUCA VICTOR ALEJANDRO</t>
-        </is>
-      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
         <v>2024112382</v>
       </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>ONTIVEROS HERRERA GABRIEL</t>
-        </is>
-      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
         <v>2021212211</v>
       </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>COILA BALDERRAMA DANIELA TATIANA</t>
-        </is>
-      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
         <v>2026119791</v>
       </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>PEÑA POTOSI ROMINA MADELEN</t>
-        </is>
-      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
         <v>2023116180</v>
       </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>CANO RUIZ MARIFER</t>
-        </is>
-      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
         <v>2026114366</v>
       </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>GONZALES ALIAGA JOSE GUILLERMO</t>
-        </is>
-      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
         <v>2024112285</v>
       </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>GUTIERREZ PANIQUE MIKAELA</t>
-        </is>
-      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
         <v>2023112729</v>
       </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>DURAN SOLETO FERNANDO ANDRE</t>
-        </is>
-      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
         <v>2023111552</v>
       </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>OVANDO MURILLO MAYA</t>
-        </is>
-      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
         <v>2023110670</v>
       </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>GUTIERREZ FERNANDEZ JOSE CARLOS</t>
-        </is>
-      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
         <v>2024113664</v>
       </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>BRUUN RUIZ MARIA RAQUEL</t>
-        </is>
-      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
         <v>2026116113</v>
       </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>BALDIVIEZO NAVARRO THAI ISABELA</t>
-        </is>
-      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
         <v>2026112550</v>
       </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>TORRICO SCHUGAIR YASSER</t>
-        </is>
-      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
         <v>2024116647</v>
       </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>CASTRO RIOS EDWIN FABRIZZIO</t>
-        </is>
-      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
         <v>2021116549</v>
       </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>LOPEZ JIMENEZ MARIA PIA</t>
-        </is>
-      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
         <v>2025112807</v>
       </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>DURÁN SANCHEZ MARCELO ANGEL</t>
-        </is>
-      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
         <v>2026110662</v>
       </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>VILLENA PARADA JORGE ENRIQUE</t>
-        </is>
-      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
         <v>2025111690</v>
       </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>CASTILLA COBO FERNANDA LUCILA</t>
-        </is>
-      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
         <v>2020210983</v>
       </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>LAURA PACO NICOLE GABRIELA</t>
-        </is>
-      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
         <v>2026116270</v>
       </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>RADONICH LORIA RENATA</t>
-        </is>
-      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
         <v>2026113394</v>
       </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>MONTERO MENACHO RICARDO</t>
-        </is>
-      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
         <v>2022110153</v>
       </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>CABEZAS ORELLANA ANGEL</t>
-        </is>
-      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
         <v>2024210023</v>
       </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>SOLIZ AVILA MARIA LAURA</t>
-        </is>
-      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
         <v>2024112129</v>
       </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>PUTARE HUARACHI HOREMI</t>
-        </is>
-      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
         <v>2026114901</v>
       </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>JUSTINIANO ROCA JOSE CARLO</t>
-        </is>
-      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
         <v>2022111613</v>
       </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>TEJERINA ORELLANA EMILY</t>
-        </is>
-      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
         <v>2022112652</v>
       </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>ROMERO VALDIVIA BRENDA</t>
-        </is>
-      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
         <v>2026116610</v>
       </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>GALLARDO VERA SANTOS DANILO</t>
-        </is>
-      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
         <v>2026114129</v>
       </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>LENS TERRAZAS LUCIA</t>
-        </is>
-      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
         <v>2026115061</v>
       </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>MELGAR SANTA CRUZ AITANA</t>
-        </is>
-      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
         <v>2025113340</v>
       </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>PARADA RUIZ JOSE GABRIEL</t>
-        </is>
-      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
         <v>2022110722</v>
       </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>PERDRIEL PINCKERTH YARA SARAI</t>
-        </is>
-      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
         <v>2025116675</v>
       </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>ASCARRUNZ LOBO CAMILA</t>
-        </is>
-      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
         <v>2023116741</v>
       </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>MUSTAFA PEÑA SAID RASHIT</t>
-        </is>
-      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
         <v>2025110731</v>
       </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>AÑEZ RUIZ MARIA RENÉ</t>
-        </is>
-      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
         <v>2026118159</v>
       </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>BASMA OSINAGA MATIA</t>
-        </is>
-      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
         <v>2022113594</v>
       </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>ESCUDERO BASCARY AGUSTINA</t>
-        </is>
-      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
         <v>2021112489</v>
       </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>VACA MANJON IVANA</t>
-        </is>
-      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
         <v>2022111176</v>
       </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>CASTILLO ROSALES DANIELA MICHELLE</t>
-        </is>
-      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
         <v>2019118491</v>
       </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>ARRAZOLA TORRES EDUARDO</t>
-        </is>
-      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
         <v>2026116296</v>
       </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>ROJAS PAZ VALERIA</t>
-        </is>
-      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
         <v>2025112980</v>
       </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>SOLIZ VEIZAGA SARA PRISCILA</t>
-        </is>
-      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
         <v>2024116337</v>
       </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>ANTELO SANDOVAL MARIANA</t>
-        </is>
-      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
         <v>2021211631</v>
       </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>VIDAL BUSTAMANTE BENJAMIN</t>
-        </is>
-      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
         <v>2024111831</v>
       </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>MAMANI ORTIZ ROSA ELENA</t>
-        </is>
-      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
         <v>2022111761</v>
       </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>CESPEDES MENDIETA ALVARO DANIEL</t>
-        </is>
-      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
         <v>2026113378</v>
       </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>ARAMAYO CLAVIJO DIEGO ALEJANDRO</t>
-        </is>
-      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
         <v>2023110297</v>
       </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>GUTIERREZ RODRIGUEZ VICENTE ANGEL</t>
-        </is>
-      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
         <v>2026119040</v>
       </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>PADILLA BARBERY MARIA JOSE</t>
-        </is>
-      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
         <v>2026118931</v>
       </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>LOPEZ OLGUIN SAMUEL</t>
-        </is>
-      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
         <v>2022113586</v>
       </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>JIMENEZ MENDEZ SOPHIA</t>
-        </is>
-      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
         <v>2026113581</v>
       </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>MORALES ARCIENEGA LUANA CRISTINA</t>
-        </is>
-      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
         <v>2023211930</v>
       </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>JUSTINIANO VACA SEBASTIAN</t>
-        </is>
-      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
         <v>2026111901</v>
       </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>ROCA JUSTINIANO MARIA VICTORIA</t>
-        </is>
-      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
         <v>2019113686</v>
       </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>SANABRIA VERAZAIN LUIS GONZALO</t>
-        </is>
-      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
         <v>2023114845</v>
       </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>AGUIRRE CHAVEZ LAURA</t>
-        </is>
-      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
         <v>2025114281</v>
       </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>MONTENEGRO BELTRAN ARIANNE</t>
-        </is>
-      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
         <v>2024116507</v>
       </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>ECHALAR PEDRAZAS NICOLAS</t>
-        </is>
-      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
         <v>2023110742</v>
       </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>JUSTINIANO ARCE DAMARIS FIORELA</t>
-        </is>
-      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
         <v>2026114773</v>
       </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>ZAPATA FRANZHEK ANDRES</t>
-        </is>
-      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
         <v>2021111911</v>
       </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>ALVARADO ROJAS JHONNY CELSO</t>
-        </is>
-      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
         <v>2026116822</v>
       </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>OSUNA GIL MARTINA</t>
-        </is>
-      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
         <v>2026114919</v>
       </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>PONCE KINN LUCIANA</t>
-        </is>
-      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
         <v>2015110381</v>
       </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>GUTIERREZ FERNANDEZ ANA BELEN</t>
-        </is>
-      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
         <v>2023110556</v>
       </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>VELEZ MORENO FABRIZZIO</t>
-        </is>
-      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
         <v>2022110927</v>
       </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>ALVAREZ EID YANISSA</t>
-        </is>
-      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
         <v>2025117493</v>
       </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>CAMACHO FLORES ROSALYN</t>
-        </is>
-      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
         <v>2025114923</v>
       </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>LEINER CAMACHO BRISA FILOMENA</t>
-        </is>
-      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
         <v>2023111561</v>
       </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>BRUCKNER AGUILERA ANITA</t>
-        </is>
-      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
         <v>2025116497</v>
       </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>MAMANI JANKO YANKARLA</t>
-        </is>
-      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
         <v>2023115213</v>
       </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>CHAVEZ NIEME MARIANO</t>
-        </is>
-      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
         <v>2022116194</v>
       </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>SARAVIA OCHOA GABRIELA ADRIANA</t>
-        </is>
-      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
         <v>2021112250</v>
       </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>ESCOBAR VELIZ VALERIA</t>
-        </is>
-      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
         <v>2022110307</v>
       </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>CUELLAR RIVERO CAROLINA</t>
-        </is>
-      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
         <v>2026111014</v>
       </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>MORALES VALDEZ CAROLINA DESSIRE</t>
-        </is>
-      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
         <v>2024113168</v>
       </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>BLANCO CHOQUE MIREYA</t>
-        </is>
-      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
         <v>2023110131</v>
       </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>ARROYO SALAZAR URSSY ADRIANA</t>
-        </is>
-      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
         <v>2023116490</v>
       </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>MORENO VACA JOHAN FERNANDO</t>
-        </is>
-      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
         <v>2024111327</v>
       </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>ZAMORA CALLISAYA BRAYAN</t>
-        </is>
-      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
         <v>2024110355</v>
       </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>SAUCEDO PEREZ LILIANA</t>
-        </is>
-      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
         <v>2026111073</v>
       </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>NUÑEZ ARANO BRIANA</t>
-        </is>
-      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
         <v>2022115619</v>
       </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>LONGARIC ARCE ROGER ALEJANDRO</t>
-        </is>
-      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
         <v>2025115466</v>
       </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>MONTAÑO RIVERA PAULA CAMILA</t>
-        </is>
-      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
         <v>2025113820</v>
       </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>ALVAREZ CAMACHO MARIANA RAQUEL</t>
-        </is>
-      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
         <v>2022115350</v>
       </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>MONTES CHAVEZ LUCAS ANDRES</t>
-        </is>
-      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
         <v>2023111137</v>
       </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>CABRERA DAZA RONAN ERNESTO</t>
-        </is>
-      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
         <v>2023210780</v>
       </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>CHALI ZUAZO MARIA JOSE</t>
-        </is>
-      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
         <v>2024112633</v>
       </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>CHAVEZ ROCHA JOEL AMERICO</t>
-        </is>
-      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
         <v>2026119350</v>
       </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>CASTILLO AVILA MEGAN STEFANI</t>
-        </is>
-      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
         <v>2026119872</v>
       </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>UJKA VARGAS ADAM</t>
-        </is>
-      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
         <v>2024116396</v>
       </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>BASURCO ESQUIVEL MARIA ELISA</t>
-        </is>
-      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
         <v>2022116640</v>
       </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>GUTIERREZ SILES RONY GABRIEL</t>
-        </is>
-      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
         <v>2022110919</v>
       </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>PEREZ ROJAS PAZ NAIARA</t>
-        </is>
-      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
         <v>2025112050</v>
       </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>VEREMEENCO BLANCO BRUNO</t>
-        </is>
-      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
         <v>2026110506</v>
       </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>URENDA FLORES MOISES</t>
-        </is>
-      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
         <v>2026113297</v>
       </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>RIOS FLORES ARIANE LOURDES</t>
-        </is>
-      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
         <v>2022113411</v>
       </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>ANGULO QUIROZ ALEXANDER JOSUE</t>
-        </is>
-      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
         <v>2024114351</v>
       </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>PEREZ GRAJEDA DIANA FLAVIA</t>
-        </is>
-      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
         <v>2021114082</v>
       </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>SAAVEDRA COSTA DARINKA STEPHANIE</t>
-        </is>
-      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
         <v>2023115451</v>
       </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>GALVIS SOLANO OSWALDO</t>
-        </is>
-      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
         <v>2026114056</v>
       </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>VIRUEZ AGUILAR TYARA AIELET</t>
-        </is>
-      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
         <v>2021116450</v>
       </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>ZANKIZ NIEME FABIANA</t>
-        </is>
-      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
         <v>2021111709</v>
       </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>ROCHA MORET ARI ANTOINE</t>
-        </is>
-      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
         <v>2024114440</v>
       </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>VELASQUEZ AUAD SAMIRA</t>
-        </is>
-      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
         <v>2026112533</v>
       </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>GUZMAN GUZMAN AARON ANTONIO</t>
-        </is>
-      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
         <v>2019113520</v>
       </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>ROSSO MORENO MARCO ANTONIO</t>
-        </is>
-      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
         <v>2023113105</v>
       </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>AGUILERA SUAREZ NAIARA</t>
-        </is>
-      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
         <v>2026118442</v>
       </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>FUENTES VELEZ ISABELLA</t>
-        </is>
-      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
         <v>2022117735</v>
       </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>SALINAS ACOSTA DAPHNE NICOLE</t>
-        </is>
-      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
         <v>2026113033</v>
       </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>CASCALES SORUCO ANA BELEN</t>
-        </is>
-      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
         <v>2023117461</v>
       </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>QUINTEROS TORDOYA FABRICIO ROY</t>
-        </is>
-      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
         <v>2022110552</v>
       </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>DORADO ZELADA FABIANA VALERIA</t>
-        </is>
-      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
         <v>2026113416</v>
       </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>COCA ARANIBAR FABIO</t>
-        </is>
-      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
         <v>2023112991</v>
       </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>CARDONA MADRID LUIS FERNANDO</t>
-        </is>
-      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
         <v>2026113980</v>
       </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>RIBERA HERRERA PAUL JUNIOR</t>
-        </is>
-      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
         <v>2024115373</v>
       </c>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>VEGA PAYARES JOSE ANDRES</t>
-        </is>
-      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
         <v>2026119201</v>
       </c>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>FRANCO CHACHAQUE ALAN DOMINIC</t>
-        </is>
-      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
         <v>2024114458</v>
       </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>SERRATE MONTENEGRO MARIANA</t>
-        </is>
-      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
         <v>2026110085</v>
       </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>ORTIZ VELASQUEZ MARIA ISABEL</t>
-        </is>
-      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
         <v>2022117395</v>
       </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>GUTIERREZ OROZCO NAYETZY</t>
-        </is>
-      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
         <v>2023112630</v>
       </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>TORREZ SILVA CRISTHIAN</t>
-        </is>
-      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
         <v>2026117853</v>
       </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>CAMPBELL ORTIZ MARIA CELESTE</t>
-        </is>
-      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
         <v>2024116477</v>
       </c>
-      <c r="B375" t="inlineStr">
-        <is>
-          <t>DURAN CANELAS CHAVEZ NICOLAS</t>
-        </is>
-      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
         <v>2023110106</v>
       </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>SEMPERTEGUI NAVIA JOSE MIGUEL</t>
-        </is>
-      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
         <v>2024115594</v>
       </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>ARIAS ROMERO KAROL VIVIANNE</t>
-        </is>
-      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
         <v>2020117266</v>
       </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>SALVATIERRA LANDIVAR FABIANA</t>
-        </is>
-      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
         <v>2026118299</v>
       </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>FUENTES HERNANDEZ JOHAN DAVID</t>
-        </is>
-      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
         <v>2026115524</v>
       </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>PARADA GUTIERREZ JOSE JAIRO</t>
-        </is>
-      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
         <v>2022112105</v>
       </c>
-      <c r="B381" t="inlineStr">
-        <is>
-          <t>GANDARILLAS FERRUFINO JUAN SEBASTIAN</t>
-        </is>
-      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
         <v>2024111718</v>
       </c>
-      <c r="B382" t="inlineStr">
-        <is>
-          <t>COPAS LEDEZMA MARIA JOSE</t>
-        </is>
-      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
         <v>2025114974</v>
       </c>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>HURTADO MORENO JUAN MARIO</t>
-        </is>
-      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
         <v>2026114412</v>
       </c>
-      <c r="B384" t="inlineStr">
-        <is>
-          <t>GUTIERREZ FRANCO MARA FERNANDA</t>
-        </is>
-      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
         <v>2026112932</v>
       </c>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>TERRAZAS REA PAULA</t>
-        </is>
-      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
         <v>2023113393</v>
       </c>
-      <c r="B386" t="inlineStr">
-        <is>
-          <t>HURTADO RIVERO LUIS FELIPE</t>
-        </is>
-      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
         <v>2025115831</v>
       </c>
-      <c r="B387" t="inlineStr">
-        <is>
-          <t>AGUILERA JUSTINIANO LEONARDO MARIANO</t>
-        </is>
-      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
         <v>2024112889</v>
       </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>NOYA DURAN LAURA ISABEL</t>
-        </is>
-      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
         <v>2024112757</v>
       </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>SERRATE ZAMBRANA JOSE GABRIEL</t>
-        </is>
-      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
         <v>2026110697</v>
       </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>GUTIERREZ FIERRO THIAGO</t>
-        </is>
-      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
         <v>2026112690</v>
       </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>IBAÑEZ MARTINEZ LUCIANA OCTAVIA</t>
-        </is>
-      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
         <v>2025112866</v>
       </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>PARRAGA GUPPY BENJAMIN</t>
-        </is>
-      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
         <v>2022112717</v>
       </c>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>JUSTINIANO MERCADO NOELIA</t>
-        </is>
-      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
         <v>2026116717</v>
       </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>GUZMAN GUILLEN IRMA DIANA</t>
-        </is>
-      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
         <v>2024116001</v>
       </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>ESPINOZA PEREZ LAURA SOFIA</t>
-        </is>
-      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
         <v>2024116353</v>
       </c>
-      <c r="B396" t="inlineStr">
-        <is>
-          <t>CHIRINO ZUNA ALVARO NICOLAS</t>
-        </is>
-      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
         <v>2022113888</v>
       </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>JUSTINIANO GUTIERREZ CIDIA IVONNE</t>
-        </is>
-      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
         <v>2023112818</v>
       </c>
-      <c r="B398" t="inlineStr">
-        <is>
-          <t>FERREIRA TOYOSATO KEIKO CHIARA</t>
-        </is>
-      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
         <v>2026112886</v>
       </c>
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>PEÑARANDA GUTIERREZ CARLA DANIELA</t>
-        </is>
-      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
         <v>2026115613</v>
       </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>RUIZ GUZMAN LUCIANA</t>
-        </is>
-      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
         <v>2025212437</v>
       </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>CORTEZ CORTEZ ANDREA</t>
-        </is>
-      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
         <v>2025111045</v>
       </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>LOPEZ SALEK SOFIA ELIANA</t>
-        </is>
-      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
         <v>2025111771</v>
       </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>TUFIÑO DURAN AGUSTIN</t>
-        </is>
-      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
         <v>2024212140</v>
       </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>WELZEL ZEA O'PHELAN ANA MARIA</t>
-        </is>
-      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
         <v>2022114337</v>
       </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>AÑEZ RUIZ FAVIO CESAR</t>
-        </is>
-      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
         <v>2023117101</v>
       </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>AGUILERA FERNANDEZ MARIA JULIA</t>
-        </is>
-      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
         <v>2021110648</v>
       </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>PRUDENCIO BRUUN RODRIGO</t>
-        </is>
-      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
         <v>2026119741</v>
       </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>SOTO MUÑOZ FABIAN</t>
-        </is>
-      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
         <v>2022112121</v>
       </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>ROSALES GAY GUADALUPE</t>
-        </is>
-      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
         <v>2025112238</v>
       </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>LANDIVAR JUSTINIANO JOSÉ MIGUEL</t>
-        </is>
-      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
         <v>2025113170</v>
       </c>
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>ROCHA VARGAS LEONARDO ALEXANDER</t>
-        </is>
-      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
         <v>2025113901</v>
       </c>
-      <c r="B412" t="inlineStr">
-        <is>
-          <t>ZAVALETA BATES JOE CARLOS</t>
-        </is>
-      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
         <v>2023210151</v>
       </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>MOSCOSO VARGAS ISABEL</t>
-        </is>
-      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
         <v>2022116011</v>
       </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>DOMINGUEZ RUIZ MAITE</t>
-        </is>
-      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
         <v>2026110611</v>
       </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>RIVERA SEMPERTEGUI NICOLE MONSERRAT</t>
-        </is>
-      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
         <v>2025114168</v>
       </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>CAMACHO VARGAS GERMAN FARID</t>
-        </is>
-      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
         <v>2025116756</v>
       </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>PADILLA LA FUENTE YASMIN ARIELY</t>
-        </is>
-      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
         <v>2024111254</v>
       </c>
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>SUAREZ GUILLEN INES</t>
-        </is>
-      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
         <v>2025210850</v>
       </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>RIBERA AGUIRRE MARILE</t>
-        </is>
-      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
         <v>2025110855</v>
       </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>SAUCEDO VALDA FREDDY FABRICIO</t>
-        </is>
-      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
         <v>2026110174</v>
       </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>SALDIAS RUEDA LUIS FERNANDO</t>
-        </is>
-      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
         <v>2026118566</v>
       </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>LASERNA OLGUIN VALENTINA</t>
-        </is>
-      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
         <v>2024113192</v>
       </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>MENA ALVAREZ FABIOLA MARISEL</t>
-        </is>
-      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
         <v>2026115362</v>
       </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>HURTADO RIVERA SEBASTIAN</t>
-        </is>
-      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
         <v>2025113579</v>
       </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>LOPEZ PATRONI KIARA</t>
-        </is>
-      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
         <v>2026210926</v>
       </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>MEJIA PARDO CARLOS ANDRÉS</t>
-        </is>
-      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
         <v>2023111901</v>
       </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>ESCOBAR CORDERO JUAN ANDRE</t>
-        </is>
-      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
         <v>2022211286</v>
       </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>AGUILAR ARCE JONATHAN</t>
-        </is>
-      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
         <v>2022211901</v>
       </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>ZURITA CARDENAS PABLO ANDRES</t>
-        </is>
-      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
         <v>2023111897</v>
       </c>
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>PEREZ ROJAS PAZ FRANCISCO</t>
-        </is>
-      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
         <v>2024116159</v>
       </c>
-      <c r="B431" t="inlineStr">
-        <is>
-          <t>AÑEZ VELEZ JUAN CARLOS</t>
-        </is>
-      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
         <v>2024114342</v>
       </c>
-      <c r="B432" t="inlineStr">
-        <is>
-          <t>PARAVICINI MANSILLA MARCO EFRAIN</t>
-        </is>
-      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
         <v>2018115766</v>
       </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>VARGAS GONZALES JEAN MARCO</t>
-        </is>
-      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
         <v>2025112301</v>
       </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>APAZA OROZCO MARTIN NICOLAS</t>
-        </is>
-      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
         <v>2024115624</v>
       </c>
-      <c r="B435" t="inlineStr">
-        <is>
-          <t>SALAS NUÑEZ NAYELI</t>
-        </is>
-      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
         <v>2022116470</v>
       </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>CAMPERO SANCHEZ FLAVIA</t>
-        </is>
-      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
         <v>2024113877</v>
       </c>
-      <c r="B437" t="inlineStr">
-        <is>
-          <t>MEDINA SOTOMAYOR MARIELA</t>
-        </is>
-      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
         <v>2026116393</v>
       </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>CORTEZ PESSOA DIANA</t>
-        </is>
-      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
         <v>2025111207</v>
       </c>
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>PAZ MENDEZ JUAN MARCELO</t>
-        </is>
-      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
         <v>2025111452</v>
       </c>
-      <c r="B440" t="inlineStr">
-        <is>
-          <t>FLORES ROMERO JHOAN NICOLAS</t>
-        </is>
-      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
         <v>2026110573</v>
       </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>QUIROZ MONTAÑO ALIM MANUEL</t>
-        </is>
-      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
         <v>2026118574</v>
       </c>
-      <c r="B442" t="inlineStr">
-        <is>
-          <t>TAVERA TAPIA TADEO ALEJANDRO</t>
-        </is>
-      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
         <v>2025111304</v>
       </c>
-      <c r="B443" t="inlineStr">
-        <is>
-          <t>CHINCHE VASQUEZ ROGER GABRIEL</t>
-        </is>
-      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
         <v>2022114973</v>
       </c>
-      <c r="B444" t="inlineStr">
-        <is>
-          <t>HOLTERS ZABALA WERNER</t>
-        </is>
-      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
         <v>2024212123</v>
       </c>
-      <c r="B445" t="inlineStr">
-        <is>
-          <t>REESE JIMENEZ ROBERT</t>
-        </is>
-      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
         <v>2022117778</v>
       </c>
-      <c r="B446" t="inlineStr">
-        <is>
-          <t>JAVIER ARACELY</t>
-        </is>
-      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
         <v>2019111098</v>
       </c>
-      <c r="B447" t="inlineStr">
-        <is>
-          <t>JRMLER MONTAÑO RENE ANDRES</t>
-        </is>
-      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
         <v>2026111821</v>
       </c>
-      <c r="B448" t="inlineStr">
-        <is>
-          <t>GILES CHAVARRIA ALISSON CAMILA</t>
-        </is>
-      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
         <v>2026119589</v>
       </c>
-      <c r="B449" t="inlineStr">
-        <is>
-          <t>MENDEZ SANCHEZ KATHERIN</t>
-        </is>
-      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
         <v>2026117101</v>
       </c>
-      <c r="B450" t="inlineStr">
-        <is>
-          <t>ESCALANTE CLAROS JESSICA</t>
-        </is>
-      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
         <v>2024111157</v>
       </c>
-      <c r="B451" t="inlineStr">
-        <is>
-          <t>REINAGA PACO ROLANDO</t>
-        </is>
-      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
         <v>2024117392</v>
       </c>
-      <c r="B452" t="inlineStr">
-        <is>
-          <t>GUARICOMA COSTAS PAULA ANDREA</t>
-        </is>
-      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
         <v>2026110191</v>
       </c>
-      <c r="B453" t="inlineStr">
-        <is>
-          <t>SANCHEZ AVIRARI DAMARIS</t>
-        </is>
-      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
         <v>2024116892</v>
       </c>
-      <c r="B454" t="inlineStr">
-        <is>
-          <t>ROCHA VIDAL SAMUEL</t>
-        </is>
-      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
         <v>2023112061</v>
       </c>
-      <c r="B455" t="inlineStr">
-        <is>
-          <t>VARGAS CUELLAR CAMILA ANGHELINA</t>
-        </is>
-      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
         <v>2026212520</v>
       </c>
-      <c r="B456" t="inlineStr">
-        <is>
-          <t>DIEZ DE MEDINA MARIN ADRIAN</t>
-        </is>
-      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
         <v>2022114124</v>
       </c>
-      <c r="B457" t="inlineStr">
-        <is>
-          <t>BAKRY NACIF NASHWA</t>
-        </is>
-      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
         <v>2024115047</v>
       </c>
-      <c r="B458" t="inlineStr">
-        <is>
-          <t>RIBERA GIL LUCIANA</t>
-        </is>
-      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
         <v>2025111541</v>
       </c>
-      <c r="B459" t="inlineStr">
-        <is>
-          <t>HERRERA GUZMAN ANTONY</t>
-        </is>
-      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
         <v>2026119970</v>
       </c>
-      <c r="B460" t="inlineStr">
-        <is>
-          <t>CONDORI COLQUE MARAHI ELIZABETH</t>
-        </is>
-      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
         <v>2025112319</v>
       </c>
-      <c r="B461" t="inlineStr">
-        <is>
-          <t>TERCEROS GARECA DAVID MATEO</t>
-        </is>
-      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
         <v>2024112480</v>
       </c>
-      <c r="B462" t="inlineStr">
-        <is>
-          <t>ANTELO YNCLAN BRUNA</t>
-        </is>
-      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
         <v>2025111797</v>
       </c>
-      <c r="B463" t="inlineStr">
-        <is>
-          <t>CAYE CABRERA JAVIER ALEJANDRO</t>
-        </is>
-      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
         <v>2025110863</v>
       </c>
-      <c r="B464" t="inlineStr">
-        <is>
-          <t>ROMERO AZURDUY IAN FRANCO</t>
-        </is>
-      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
         <v>2026113548</v>
       </c>
-      <c r="B465" t="inlineStr">
-        <is>
-          <t>PARRA DELGADILLO ROGER GABRIEL</t>
-        </is>
-      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
         <v>2026110034</v>
       </c>
-      <c r="B466" t="inlineStr">
-        <is>
-          <t>CALICHO ALARCON JOSH KEN</t>
-        </is>
-      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
         <v>2024110851</v>
       </c>
-      <c r="B467" t="inlineStr">
-        <is>
-          <t>ALVAREZ BARBERY DUNIA</t>
-        </is>
-      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
         <v>2025111371</v>
       </c>
-      <c r="B468" t="inlineStr">
-        <is>
-          <t>RUEDA SUAREZ MIGUEL ANDRES</t>
-        </is>
-      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
         <v>2026113670</v>
       </c>
-      <c r="B469" t="inlineStr">
-        <is>
-          <t>SUAREZ DE LA JAILLE ERICK</t>
-        </is>
-      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
         <v>2024112099</v>
       </c>
-      <c r="B470" t="inlineStr">
-        <is>
-          <t>HURTADO MONTOYA CAMILA</t>
-        </is>
-      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
         <v>2024112820</v>
       </c>
-      <c r="B471" t="inlineStr">
-        <is>
-          <t>GRAGEDA FLORES KEREN</t>
-        </is>
-      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
         <v>2026119571</v>
       </c>
-      <c r="B472" t="inlineStr">
-        <is>
-          <t>CASTELLÓN CARTAGENA JOSE ALVARO</t>
-        </is>
-      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
         <v>2022115627</v>
       </c>
-      <c r="B473" t="inlineStr">
-        <is>
-          <t>PALACIOS RIVERO FRANCESCA</t>
-        </is>
-      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
         <v>2025115679</v>
       </c>
-      <c r="B474" t="inlineStr">
-        <is>
-          <t>LEAÑOS RUIZ MICHELE KERINE</t>
-        </is>
-      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
         <v>2024111785</v>
       </c>
-      <c r="B475" t="inlineStr">
-        <is>
-          <t>YAÑEZ CESPEDES FABIANA</t>
-        </is>
-      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
         <v>2025212127</v>
       </c>
-      <c r="B476" t="inlineStr">
-        <is>
-          <t>BAUSE MELGAR INGO</t>
-        </is>
-      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
         <v>2026114528</v>
       </c>
-      <c r="B477" t="inlineStr">
-        <is>
-          <t>ALVAREZ LACKOVIC BRIANNA</t>
-        </is>
-      </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
         <v>2023115019</v>
       </c>
-      <c r="B478" t="inlineStr">
-        <is>
-          <t>PERALTA ALVAREZ NOELIA</t>
-        </is>
-      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
         <v>2023117071</v>
       </c>
-      <c r="B479" t="inlineStr">
-        <is>
-          <t>VILLAFUERTE NATUSCH JUAN CARLOS</t>
-        </is>
-      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
         <v>2026111171</v>
       </c>
-      <c r="B480" t="inlineStr">
-        <is>
-          <t>IBACETA MOSCOSO RANDY</t>
-        </is>
-      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
         <v>2024113869</v>
       </c>
-      <c r="B481" t="inlineStr">
-        <is>
-          <t>CANEDO LOBOS ISABELLA</t>
-        </is>
-      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
         <v>2026120471</v>
       </c>
-      <c r="B482" t="inlineStr">
-        <is>
-          <t>ALMARAZ SUAREZ LEONARDO</t>
-        </is>
-      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
         <v>2024114237</v>
       </c>
-      <c r="B483" t="inlineStr">
-        <is>
-          <t>FOIANINI HESSELBARTH CARLO</t>
-        </is>
-      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
         <v>2025110081</v>
       </c>
-      <c r="B484" t="inlineStr">
-        <is>
-          <t>JULIO PEREIRA GEORGINA</t>
-        </is>
-      </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
         <v>2024116302</v>
       </c>
-      <c r="B485" t="inlineStr">
-        <is>
-          <t>TINEO SUJET NICOLAS</t>
-        </is>
-      </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
         <v>2026110336</v>
       </c>
-      <c r="B486" t="inlineStr">
-        <is>
-          <t>COLQUE ANTONIO ALEJANDRO GABRIEL</t>
-        </is>
-      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
         <v>2022110269</v>
       </c>
-      <c r="B487" t="inlineStr">
-        <is>
-          <t>ROMERO CRESPO EMILY VALERIA</t>
-        </is>
-      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
         <v>2024116469</v>
       </c>
-      <c r="B488" t="inlineStr">
-        <is>
-          <t>COLODRO GUTIERREZ GABRIEL</t>
-        </is>
-      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
         <v>2023112702</v>
       </c>
-      <c r="B489" t="inlineStr">
-        <is>
-          <t>DE LA QUINTANA SUAREZ SEBASTIAN FERNANDO</t>
-        </is>
-      </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
         <v>2013110022</v>
       </c>
-      <c r="B490" t="inlineStr">
-        <is>
-          <t>MENDEZ MEDINA AARON WILLANS</t>
-        </is>
-      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
         <v>2024111921</v>
       </c>
-      <c r="B491" t="inlineStr">
-        <is>
-          <t>PAZ JUSTINIANO SOFIA</t>
-        </is>
-      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
         <v>2026113467</v>
       </c>
-      <c r="B492" t="inlineStr">
-        <is>
-          <t>HUARITA RICALDI AZHIER BELEN</t>
-        </is>
-      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
         <v>2023113385</v>
       </c>
-      <c r="B493" t="inlineStr">
-        <is>
-          <t>MORENO SUAREZ ARANA BRUNA</t>
-        </is>
-      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
         <v>2026116911</v>
       </c>
-      <c r="B494" t="inlineStr">
-        <is>
-          <t>ARCE MAMANI LEONARDO</t>
-        </is>
-      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
         <v>2023117445</v>
       </c>
-      <c r="B495" t="inlineStr">
-        <is>
-          <t>APONTE GOMEZ JOSUE DANIEL</t>
-        </is>
-      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
         <v>2025114991</v>
       </c>
-      <c r="B496" t="inlineStr">
-        <is>
-          <t>COLUSSI CASARIN GABRIEL</t>
-        </is>
-      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
         <v>2026116032</v>
       </c>
-      <c r="B497" t="inlineStr">
-        <is>
-          <t>PANIAGUA HUAYTA CONSTANZA MICHELLE</t>
-        </is>
-      </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
         <v>2024111211</v>
       </c>
-      <c r="B498" t="inlineStr">
-        <is>
-          <t>RIOJA CRONENBOLD RENATA</t>
-        </is>
-      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
         <v>2022116356</v>
       </c>
-      <c r="B499" t="inlineStr">
-        <is>
-          <t>JEREZ SALVATIERRA SOL</t>
-        </is>
-      </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
         <v>2020114801</v>
       </c>
-      <c r="B500" t="inlineStr">
-        <is>
-          <t>AGUILAR LOPEZ MAYRA ADRIANA</t>
-        </is>
-      </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
         <v>2026211418</v>
-      </c>
-      <c r="B501" t="inlineStr">
-        <is>
-          <t>FERNANDEZ MAMANI SHERMIE VALERI</t>
-        </is>
       </c>
     </row>
   </sheetData>
